--- a/測定結果表.xlsx
+++ b/測定結果表.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\foolder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/773fdd1b97ca4f85/SSK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{736DD3BA-A19C-4D26-B395-2B70D54838D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{146930F9-FDF9-4271-81D1-8D21C6B6A47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1475FB3F-6C07-450D-A166-5238BBCCD174}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8880" xr2:uid="{5ACD9BC7-44F8-4362-B56F-523CB012E919}"/>
+    <workbookView xWindow="5220" yWindow="2448" windowWidth="13512" windowHeight="8880" xr2:uid="{4F125F49-75BF-47D2-9A0D-66FED1ECFFBB}"/>
   </bookViews>
   <sheets>
     <sheet name="測定結果表" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">測定結果表!$A$1:$O$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">測定結果表!$A$1:$O$105</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
   <si>
     <t>略図</t>
   </si>
@@ -63,28 +63,139 @@
     <t>差</t>
   </si>
   <si>
-    <t>シートの重ね幅 W</t>
+    <t xml:space="preserve">均平度 </t>
   </si>
   <si>
-    <t>GE-1</t>
+    <t>No.1</t>
   </si>
   <si>
-    <t>C-1</t>
+    <t>No.2</t>
   </si>
   <si>
-    <t>GE-2</t>
+    <t>No.3</t>
   </si>
   <si>
-    <t>100</t>
+    <t>No.4</t>
   </si>
   <si>
-    <t>110</t>
+    <t>No.5</t>
   </si>
   <si>
-    <t>＋10</t>
+    <t>No.6</t>
   </si>
   <si>
-    <t>0</t>
+    <t>No.7</t>
+  </si>
+  <si>
+    <t>No.8</t>
+  </si>
+  <si>
+    <t>No.9</t>
+  </si>
+  <si>
+    <t>No.10</t>
+  </si>
+  <si>
+    <t>No.11</t>
+  </si>
+  <si>
+    <t>No.12</t>
+  </si>
+  <si>
+    <t>1.418</t>
+  </si>
+  <si>
+    <t>1.400</t>
+  </si>
+  <si>
+    <t>1.409</t>
+  </si>
+  <si>
+    <t>1.415</t>
+  </si>
+  <si>
+    <t>1.419</t>
+  </si>
+  <si>
+    <t>1.421</t>
+  </si>
+  <si>
+    <t>1.412</t>
+  </si>
+  <si>
+    <t>1.403</t>
+  </si>
+  <si>
+    <t>1.416</t>
+  </si>
+  <si>
+    <t>No.13</t>
+  </si>
+  <si>
+    <t>No.14</t>
+  </si>
+  <si>
+    <t>No.15</t>
+  </si>
+  <si>
+    <t>No.16</t>
+  </si>
+  <si>
+    <t>No.17</t>
+  </si>
+  <si>
+    <t>No.18</t>
+  </si>
+  <si>
+    <t>No.19</t>
+  </si>
+  <si>
+    <t>No.20</t>
+  </si>
+  <si>
+    <t>No.21</t>
+  </si>
+  <si>
+    <t>No.22</t>
+  </si>
+  <si>
+    <t>No.23</t>
+  </si>
+  <si>
+    <t>No.24</t>
+  </si>
+  <si>
+    <t>1.406</t>
+  </si>
+  <si>
+    <t>1.404</t>
+  </si>
+  <si>
+    <t>1.410</t>
+  </si>
+  <si>
+    <t>1.411</t>
+  </si>
+  <si>
+    <t>No.25</t>
+  </si>
+  <si>
+    <t>No.26</t>
+  </si>
+  <si>
+    <t>No.27</t>
+  </si>
+  <si>
+    <t>No.28</t>
+  </si>
+  <si>
+    <t>No.29</t>
+  </si>
+  <si>
+    <t>No.30</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -262,12 +373,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -281,20 +389,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -303,15 +399,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
@@ -325,6 +412,24 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -363,7 +468,7 @@
         <xdr:cNvPr id="3" name="テキスト ボックス 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F07EDDE-8E74-0BBD-BC73-5CE09A309C98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F68858B1-BBD7-CA45-AABE-77A7EB292EFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -455,7 +560,7 @@
         <xdr:cNvPr id="4" name="直線コネクタ 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA40B5F9-7AC1-68D8-0980-9F0F7AF9AEA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A2A87E0-8BC4-2DFA-A7C9-852661308035}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -513,7 +618,7 @@
         <xdr:cNvPr id="5" name="テキスト ボックス 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11C9E966-F0C8-7A1D-C568-950B7187CFF3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9F26D9E-9C8F-9766-0FAC-5344117CB1F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -580,7 +685,7 @@
               <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
               <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
             </a:rPr>
-            <a:t>請 負 者</a:t>
+            <a:t>受 注 者</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -605,7 +710,7 @@
         <xdr:cNvPr id="6" name="テキスト ボックス 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CD68867-507D-979C-4827-BFE9D109F634}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73B6CCAB-C0E1-DA36-785D-0CB13877F29C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -664,16 +769,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>株式会社あべ建設</a:t>
-          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -697,7 +799,7 @@
         <xdr:cNvPr id="7" name="テキスト ボックス 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{052C83B0-472F-28B8-5E14-EDA58B881745}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BDDFCDE-A273-5FCB-AC20-C1721296D491}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -806,7 +908,7 @@
         <xdr:cNvPr id="8" name="テキスト ボックス 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C62BE8-4C36-300B-45B9-2C1661E821A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01D9C13C-12B2-12D1-ECAB-9E4AFF9294F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -898,7 +1000,7 @@
         <xdr:cNvPr id="9" name="テキスト ボックス 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A062122-819B-32CB-02C9-39DEE1311E60}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C606B7C-9ACE-061A-A130-57DCA3829380}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +1067,7 @@
               <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
               <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
             </a:rPr>
-            <a:t>橋面防水工</a:t>
+            <a:t>整地工</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -990,7 +1092,7 @@
         <xdr:cNvPr id="10" name="直線コネクタ 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D3F1BA9-CBD3-CFE9-15B1-C0FECDDA7E17}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{672024CB-177B-E2B1-0C41-31674D09FFF0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1048,7 +1150,7 @@
         <xdr:cNvPr id="11" name="テキスト ボックス 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24BBC4B9-2380-0B96-2C19-68301BE905BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D63E26E-9537-CFAB-CCFC-D0DB7F2D4FDE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1107,16 +1209,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>佐々木拓二　</a:t>
-          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1140,7 +1239,7 @@
         <xdr:cNvPr id="12" name="テキスト ボックス 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E563B416-4A8C-A3C9-5165-7C1B8ADCF9BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA251FBD-0BF5-6DE2-48D1-4FD0DA7E7CD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1232,7 +1331,7 @@
         <xdr:cNvPr id="13" name="直線コネクタ 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BE5CC97-C37A-390E-6701-E63BC387B16F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8D773AB-11C2-A4DE-8B9C-F2322F2785CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1290,7 +1389,7 @@
         <xdr:cNvPr id="14" name="テキスト ボックス 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9787249B-5B51-5137-2288-BBDC63B766FA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89DE73B3-1893-67AC-1074-FB676965471D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1357,7 +1456,7 @@
               <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
               <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
             </a:rPr>
-            <a:t>防水シート</a:t>
+            <a:t>整地仕上げ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1382,7 +1481,7 @@
         <xdr:cNvPr id="15" name="テキスト ボックス 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48F6385B-1CCE-768E-7743-EDAB1F271B46}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D66E40E-99E1-CF2C-C07D-4BE941BBBE9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1474,7 +1573,7 @@
         <xdr:cNvPr id="16" name="直線コネクタ 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C58617BD-9B4E-4AE4-7D5F-26909F67B725}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02F852E0-4647-86E7-7AED-F66A801BEE30}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1532,7 +1631,7 @@
         <xdr:cNvPr id="17" name="テキスト ボックス 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EC104BD-1BA6-36E7-FE5D-5141D026CACE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E614A22-5316-BB54-06B7-1C14D06BD743}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1608,98 +1707,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>267720</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>273720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>3180</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>2700</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="テキスト ボックス 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17D8E236-BBFC-D9D0-3CA8-A8141E0D8DB3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7689600" y="990000"/>
-          <a:ext cx="1922400" cy="270000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:shade val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>佐々木　拓二</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>461820</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -1713,10 +1720,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線コネクタ 18">
+        <xdr:cNvPr id="18" name="直線コネクタ 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{858A20DA-4CD6-4F7C-A9AF-890D56644654}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97A2B3E-CD13-3DD0-FA1B-63998DFC8DA7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1771,10 +1778,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="テキスト ボックス 19">
+        <xdr:cNvPr id="19" name="テキスト ボックス 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F087E8A4-CB31-D8DA-3215-E530DDC42A48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF945CB-69A2-8ADA-7BFF-C25DB2677AD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1883,10 +1890,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+        <xdr:cNvPr id="20" name="テキスト ボックス 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EB28F45-7E7A-5326-20EA-E99E9A70194C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2C60CDE-6DF6-6B1F-96B1-860DB34144BF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1979,23 +1986,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>742</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>429420</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>58552</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>344</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>464220</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="テキスト ボックス 21">
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA2185A-9E2A-AC48-7B1B-4C7D27FEB98C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BEFDD1A-34B8-5BD1-9CA4-68CEEC47D028}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2003,8 +2010,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="846000" y="1875262"/>
-          <a:ext cx="1186132" cy="327262"/>
+          <a:off x="2403000" y="6687480"/>
+          <a:ext cx="3844800" cy="540000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2048,59 +2055,22 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1984" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
               <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
             </a:rPr>
-            <a:t>－</a:t>
+            <a:t>測定結果表</a:t>
           </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>20</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>～＋</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>50</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2109,22 +2079,80 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>58552</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>742</xdr:rowOff>
+      <xdr:colOff>429420</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>497258</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>344</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>464220</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="直線コネクタ 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C81324B6-06F9-9892-58B1-E646AE52BDB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2403000" y="7227480"/>
+          <a:ext cx="3844800" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171600</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="23" name="テキスト ボックス 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB8A5630-D9D6-3F28-9C62-91386FACE78A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43D68A5D-9154-46E9-E8E2-207FD064BD51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2132,8 +2160,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2032132" y="1875262"/>
-          <a:ext cx="438706" cy="327262"/>
+          <a:off x="6824520" y="6687480"/>
+          <a:ext cx="768960" cy="540000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2177,12 +2205,1297 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>受 注 者</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>267720</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="テキスト ボックス 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78654AA0-BDB5-3420-5D74-89A9468571E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7689600" y="6687480"/>
+          <a:ext cx="1922400" cy="540000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>115380</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト ボックス 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3391B4C5-9CCC-2A6E-5F75-0C4861744073}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6507480"/>
+          <a:ext cx="961200" cy="180000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>様式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>(36)-2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>480600</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト ボックス 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FBB666D-D4E3-618F-40C6-E1E982C7DA58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7227480"/>
+          <a:ext cx="480600" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>工種</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>576720</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="テキスト ボックス 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B182F646-5E19-E240-C416-BBED348C487F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="576720" y="7227480"/>
+          <a:ext cx="2787480" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>整地工</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F72501DD-1BC1-0ABC-E4E4-A6D296BA0323}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7497480"/>
+          <a:ext cx="3364200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>267720</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7CFD9D8-9748-3B87-DAA3-966674929CE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7689600" y="7227480"/>
+          <a:ext cx="1922400" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171600</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="テキスト ボックス 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA740A17-07C5-CC5D-D3AB-D12549A84AC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="7227480"/>
+          <a:ext cx="768960" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>現場代理人</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直線コネクタ 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7F7292A-37FF-B201-3DCB-BC02BDE473DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="7497480"/>
+          <a:ext cx="2787480" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>576720</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="テキスト ボックス 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C192FED-0C58-E255-430F-1480EFF0FBF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="576720" y="7497480"/>
+          <a:ext cx="2787480" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>整地仕上げ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>480600</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="テキスト ボックス 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0524F4CA-38A6-0A3F-6EFF-7746D1578175}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7497480"/>
+          <a:ext cx="480600" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>細別</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="直線コネクタ 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDD53AE0-78EE-8073-A009-DC8A5D71490E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7767480"/>
+          <a:ext cx="3364200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171600</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="テキスト ボックス 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73C8643-F2A4-5769-F09C-1EC75EAE3FB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="7497480"/>
+          <a:ext cx="768960" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>測 定 者</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="直線コネクタ 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DF586B9-611D-2336-F8B9-AC244C08B530}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="7767480"/>
+          <a:ext cx="2787480" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>141720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>497040</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>3000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="テキスト ボックス 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3742386E-08AD-8367-516E-109CB9676832}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="12699480"/>
+          <a:ext cx="7416000" cy="288000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>注</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>基準高については、設計図書において表示されているものについて記入する。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1132800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>1140</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="テキスト ボックス 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F73DC246-D79E-0386-3AAC-93BC6E637CFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8554680" y="7767480"/>
+          <a:ext cx="1057320" cy="288000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>単位：</a:t>
+          </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -2207,23 +3520,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>344</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>429420</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>58552</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>327606</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>464220</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="テキスト ボックス 23">
+        <xdr:cNvPr id="39" name="テキスト ボックス 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B26F934-9F2D-8655-59D4-0A09FFD4A6B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9199489C-A322-8092-B220-80C0CFB6E00B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2231,8 +3544,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="846000" y="2202524"/>
-          <a:ext cx="1186132" cy="327262"/>
+          <a:off x="2403000" y="13194960"/>
+          <a:ext cx="3844800" cy="540000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2276,59 +3589,22 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="800080"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1984" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
               <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
             </a:rPr>
-            <a:t>－</a:t>
+            <a:t>測定結果表</a:t>
           </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="800080"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>16</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="800080"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>～＋</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="800080"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            </a:rPr>
-            <a:t>40</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="800080"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2337,22 +3613,80 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>58552</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>344</xdr:rowOff>
+      <xdr:colOff>429420</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>497258</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>327606</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>464220</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C33B075-8C42-CB61-2F58-38F1284C08EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2403000" y="13734960"/>
+          <a:ext cx="3844800" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171600</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="テキスト ボックス 24">
+        <xdr:cNvPr id="41" name="テキスト ボックス 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{559E5C94-3FDA-ECFC-C287-87255C271EA0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D950C0EE-A952-1187-4127-F64AEFFA3816}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2360,8 +3694,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2032132" y="2202524"/>
-          <a:ext cx="438706" cy="327262"/>
+          <a:off x="6824520" y="13194960"/>
+          <a:ext cx="768960" cy="540000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2405,12 +3739,1297 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>受 注 者</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>267720</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="テキスト ボックス 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{719204A7-9862-9759-3B6E-33C2ADD0A2FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7689600" y="13194960"/>
+          <a:ext cx="1922400" cy="540000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>115380</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>180001</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="テキスト ボックス 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BD1C424-1DC0-F0E9-0344-7283139C3DBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13014961"/>
+          <a:ext cx="961200" cy="180000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>様式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>(36)-2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>480600</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="テキスト ボックス 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF6DA90E-8F3B-E137-F693-7513CFF5DAD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13734960"/>
+          <a:ext cx="480600" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>工種</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>576720</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="テキスト ボックス 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC425FB-9D04-D254-96FE-E4B790D0AE6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="576720" y="13734960"/>
+          <a:ext cx="2787480" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>整地工</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="直線コネクタ 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E210B028-4AF4-5AA4-B7A7-E82263B029E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14004961"/>
+          <a:ext cx="3364200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>267720</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="テキスト ボックス 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{545670F0-A5C7-8C45-E73E-EC5E693B09FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7689600" y="13734960"/>
+          <a:ext cx="1922400" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>537120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171600</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="テキスト ボックス 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BE377F8-8B26-0AF2-4D58-E51729F898A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="13734960"/>
+          <a:ext cx="768960" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>現場代理人</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="49" name="直線コネクタ 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D229CAF-4EF9-F93A-AF1B-DAE673FD3B93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="14004961"/>
+          <a:ext cx="2787480" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>576720</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269401</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="テキスト ボックス 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D93EF103-8F4F-DCF9-FF0C-86D3D1AAF265}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="576720" y="14004961"/>
+          <a:ext cx="2787480" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>整地仕上げ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>480600</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269401</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="テキスト ボックス 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05E91581-38F2-3FA9-3A4E-6CC9C363C52E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14004961"/>
+          <a:ext cx="480600" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>細別</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331440</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="直線コネクタ 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B37D0AFE-094B-C995-3F3F-2E9C5BB62252}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14274960"/>
+          <a:ext cx="3364200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>266101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171600</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269401</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="テキスト ボックス 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD13C8A6-C969-3FAD-2BB1-8D75652C041E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="14004961"/>
+          <a:ext cx="768960" cy="270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>測 定 者</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461820</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="54" name="直線コネクタ 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D91DBC-AA25-F9A6-2CDF-FC4027A7DEAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6824520" y="14274960"/>
+          <a:ext cx="2787480" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6480">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>134099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>497040</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>284939</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="テキスト ボックス 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0413807-F578-D2E6-9DFA-887B198FB347}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="19206959"/>
+          <a:ext cx="7416000" cy="288000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>注</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>基準高については、設計図書において表示されているものについて記入する。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1132800</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>269400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3180</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>283080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="テキスト ボックス 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEF159AE-3FDE-9991-6229-C8C38C913725}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8554680" y="14274960"/>
+          <a:ext cx="1057320" cy="288000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="992" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+              <a:ea typeface="ＭＳ 明朝" panose="02020609040205080304" pitchFamily="17" charset="-128"/>
+            </a:rPr>
+            <a:t>単位：</a:t>
+          </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="992" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -2732,11 +5351,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30841423-EB24-4DAD-82A8-6ECC3574382F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5A8E31-8EA7-42DB-8565-813F2D78D205}">
+  <dimension ref="A1:O105"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.09765625" customWidth="1"/>
@@ -2761,549 +5377,1652 @@
     <row r="3" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="4" spans="1:14" ht="21.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="5" spans="1:14" ht="22.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
+      <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="1" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="16" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="1"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="1"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="16"/>
     </row>
     <row r="9" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="5"/>
+      <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="10.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" ht="10.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="2"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="2"/>
+      <c r="A24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="2"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="2"/>
+      <c r="A26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="2"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="2"/>
+      <c r="A28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="2"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="2"/>
+      <c r="A30" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="2"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="2"/>
+      <c r="A32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="4"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="3"/>
     </row>
     <row r="34" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:14" ht="2.85" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="36" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="37" spans="1:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="38" spans="1:14" ht="21.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="39" spans="1:14" ht="21.45" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" spans="1:14" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="16"/>
+    </row>
+    <row r="43" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="16"/>
+    </row>
+    <row r="44" spans="1:14" ht="25.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N44" s="17"/>
+    </row>
+    <row r="45" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="1:14" ht="22.65" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="70" spans="1:14" ht="2.85" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="71" spans="1:14" ht="14.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="72" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="73" spans="1:14" ht="21.45" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="74" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="75" spans="1:14" ht="22.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="N75" s="2"/>
+    </row>
+    <row r="76" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="25.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="16"/>
+    </row>
+    <row r="78" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="16"/>
+    </row>
+    <row r="79" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N79" s="17"/>
+    </row>
+    <row r="80" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B82" s="5"/>
+      <c r="C82" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B84" s="5"/>
+      <c r="C84" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
+      <c r="M85" s="7"/>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" s="5"/>
+      <c r="C86" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
+      <c r="M89" s="7"/>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
+      <c r="M91" s="7"/>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="1:14" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="1:15" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="7"/>
+      <c r="M97" s="7"/>
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="1:15" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:15" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7"/>
+      <c r="M99" s="7"/>
+      <c r="N99" s="1"/>
+    </row>
+    <row r="100" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="1"/>
+    </row>
+    <row r="101" spans="1:15" ht="11.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+      <c r="M101" s="7"/>
+      <c r="N101" s="1"/>
+    </row>
+    <row r="102" spans="1:15" ht="10.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="1"/>
+    </row>
+    <row r="103" spans="1:15" ht="11.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="7"/>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7"/>
+      <c r="M103" s="7"/>
+      <c r="N103" s="3"/>
+    </row>
+    <row r="104" spans="1:15" ht="22.95" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="105" spans="1:15" ht="2.85" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="O105" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="D14:D15"/>
+  <mergeCells count="36">
+    <mergeCell ref="C16:C17"/>
     <mergeCell ref="N6:N9"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="N41:N44"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="N76:N79"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C88:C89"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236215" right="0.59055118110236215" top="0.59055118110236215" bottom="0.59055118110236215" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="35" max="14" man="1"/>
+    <brk id="70" max="14" man="1"/>
+    <brk id="105" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>